--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>46065</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45524</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45846</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45904</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45951</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45781</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>44742</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44802</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44876</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44462</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>45299</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44564</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44672</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>45610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45098</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>45551</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>45931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45716</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44781</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>46000</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44789</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44896</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>46281</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45849</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>45853</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44804</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45147</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>46211</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44846</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44739</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>44725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>44864</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>44463</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44549</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44688</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44725</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44500</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44462</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44491</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>44572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44866</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45604</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44581</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45107</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45561</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45664</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44978</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44630</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45636</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44956</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45281</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45281</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>45198</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>44690</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>45240</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>44585</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>45282</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45455</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45740</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>44727</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45232</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45435</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44609</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45107</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>45622</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>45599</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45811</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45604</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45638</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45145</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45138</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45063</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44960</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>46014</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45190</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>46043</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44840</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         <v>45567</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>45170</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45566</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46136</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45561</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>45365</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45561</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>46073</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45905</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>46071</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>45911</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>45411</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>46098</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>46084</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>46087</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45670</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>46034</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45811</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45098</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>46069</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45569</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44732</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>45925</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45925</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>44982</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45929</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>46051</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44882</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45236</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45930</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>45936</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45939</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>46091</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>45945</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>46044</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44711</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45006</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>46153</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44935</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46153</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45960</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45961</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45964</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44869</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45321</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>46154</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45971</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45175</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45604</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45604</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>45484</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>46155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45638</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45604</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45527</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45527</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45985</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45604</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45527</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45342</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45960</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45574</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45992</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45993</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45265</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45154</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45268</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>46087</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45330</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45411</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45411</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>46163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>46163</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>46163</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>46164</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>46000</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45576</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45411</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45411</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45398</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44965</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45628</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45427</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45063</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>46014</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46167</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44992</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45939</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>46026</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>46027</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>46030</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>46031</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>46031</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>46031</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46034</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46036</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>46036</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>46036</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>46036</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45110</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>46037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>44463</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45455</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>46042</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>44462</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>46045</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>46045</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>45432</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>46051</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45366</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45953</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>46010</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45971</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44812</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44691</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46057</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46076</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>46057</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>44908</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>46065</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>46064</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>45005</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44532</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>46076</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45469</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>46076</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>46076</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45665</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>44595</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45644</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>46077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46083</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45638</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>46087</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45719</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>46190</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46092</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>46083</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>46093</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>46094</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46094</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44817</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46098</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>46098</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45334</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46191</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>46092</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>46196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45546</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45622</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>44784</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>46119</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>46076</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>46092</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45247</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>45201</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>46092</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>46094</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>46204</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>46136</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45561</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45574</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>45604</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45771</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44784</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>45140</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45453</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44811</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>46066</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45411</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>46254</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45527</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45442</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>44643</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>46211</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45628</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45232</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44953</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44964</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45520</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45182</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>46261</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>46262</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>45232</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>46174</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44809</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44788</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44748</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>45171</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>45783</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45596</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>46273</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46275</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46234</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45428</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>46275</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45432</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45700</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45790</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46283</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45365</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45666</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45118</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45443</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45462</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45377</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45804</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45804</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45811</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45552</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44784</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>45771</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45820</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45825</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45855</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45855</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28738,7 +28738,7 @@
         <v>45870</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45875</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>45883</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44155</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>44071</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44585</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45391</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45720</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>46065</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45524</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45846</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45904</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45951</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44742</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44802</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44876</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45299</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44672</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44789</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45931</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44781</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45716</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45551</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>44896</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45849</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45575</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45098</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>46211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44864</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44549</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44511</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44735</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44688</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44725</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44502</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44491</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44715</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44748</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45719</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45435</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44869</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45411</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45455</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45455</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45666</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45411</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44956</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45443</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>46026</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>46030</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45282</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45118</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45462</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45334</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45377</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45604</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>46031</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>46031</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>46034</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44866</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>46037</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44595</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>46042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44972</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46045</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45138</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45971</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45905</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>46057</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>46057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46064</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>46065</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45638</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>46076</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45925</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45925</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>46076</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46076</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45930</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45145</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46083</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46077</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45569</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46087</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45936</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>46083</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>46093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46092</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45939</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>46094</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>46094</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>46098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>46098</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45398</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45811</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45576</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45552</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45604</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45811</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45453</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45954</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>46113</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>46119</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45628</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45628</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45638</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45622</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45638</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45636</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45107</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45604</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45971</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45771</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>46092</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>46092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45985</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45960</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44748</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45992</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45005</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45201</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>46084</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>46000</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45561</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45561</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>46014</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45561</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45574</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45567</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45811</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46014</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44788</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46140</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46069</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45236</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>46051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46071</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>46098</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44532</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45811</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46091</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45411</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>46153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>46154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45342</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46087</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45561</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45527</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45330</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46164</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>46163</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45140</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46163</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46163</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46167</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44992</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45855</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45870</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46076</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45665</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45484</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45771</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44630</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46191</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45875</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45644</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>46204</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45604</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45427</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45063</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44691</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>46066</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>46254</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46211</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45107</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45232</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45154</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45670</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44690</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>46262</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46261</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44727</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44711</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45247</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44732</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45366</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>44812</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45265</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45273</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>44964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45264</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46275</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>46275</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46273</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45469</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45520</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46234</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45232</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46283</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44809</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44581</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44739</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45432</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46196</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45604</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45604</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45546</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45604</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44643</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>44896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45740</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45527</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45527</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45599</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45411</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44982</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44817</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45442</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44935</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44784</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44784</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45527</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45268</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45526</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44811</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44965</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44830</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45365</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45604</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45664</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45264</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45232</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45171</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45596</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45783</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45428</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45432</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45790</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45700</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45182</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45391</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45952</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45951</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>46085</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>46065</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45524</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45846</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45904</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45951</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44742</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45781</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>44802</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>44803</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>44876</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45411</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45939</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>45299</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44672</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44789</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>44594</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45931</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45939</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44781</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45874</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>46000</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45716</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>46146</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45551</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>44896</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45849</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45853</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>45575</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         <v>46279</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45098</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>46281</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>46211</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>44846</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>44725</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44864</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44549</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44511</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>44735</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44688</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44725</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44503</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44502</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44491</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44715</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44650</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44748</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>45198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>45321</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45110</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45719</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45435</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>44882</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44869</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45411</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>45455</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45455</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45666</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45411</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>45365</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>44956</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45883</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45443</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>46026</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>46030</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45282</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45118</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45462</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45334</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45377</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45604</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>46031</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>46031</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>46034</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44840</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46036</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>46036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44866</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>46037</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44595</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>46042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44972</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46045</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45138</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45905</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45971</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45905</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>46051</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>46057</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>46057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46064</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>46065</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>45638</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>45566</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>46076</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45925</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45925</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>46076</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46076</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45930</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45145</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46083</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45804</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46077</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45569</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>46087</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45936</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>46083</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>46093</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>46092</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45939</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>46094</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>46094</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44784</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>46098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>46098</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>45398</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45811</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45576</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45182</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45552</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45604</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45811</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45453</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45954</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>46113</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>45960</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45960</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>46119</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45628</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45628</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>45006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>45638</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>45622</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15773,7 +15773,7 @@
         <v>45638</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>45636</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15919,7 +15919,7 @@
         <v>45107</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>45604</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45971</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>45771</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45411</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>46092</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>46092</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45985</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45960</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>44748</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45992</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45005</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45993</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45201</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>46084</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44896</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46073</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>46000</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45561</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45561</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
         <v>46014</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>45561</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45574</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45567</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45811</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46014</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44788</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>46140</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>46069</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45236</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45825</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>46087</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>46051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>46071</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>46098</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44532</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45811</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46091</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45411</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>46044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>46153</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>46153</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>46154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45342</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>46087</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>45561</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45527</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45330</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46164</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>46163</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45140</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46163</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>46163</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>46163</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46167</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>44992</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45855</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45870</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>44572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46076</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45665</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>45484</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45771</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>46190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44630</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>45163</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46191</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45875</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45644</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>46204</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45604</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45190</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22395,7 +22395,7 @@
         <v>45427</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45063</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44691</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>46066</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22692,7 +22692,7 @@
         <v>46254</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>46211</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22838,7 +22838,7 @@
         <v>45107</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45232</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         <v>45154</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>45622</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45670</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>44690</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23427,7 +23427,7 @@
         <v>46262</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>46261</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>44727</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44711</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>45247</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>44732</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45366</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>44812</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>45265</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>45273</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24245,7 +24245,7 @@
         <v>44964</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45264</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>46275</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>46275</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>46273</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45469</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45520</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>46234</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45232</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>46283</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>44809</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44581</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>44739</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45432</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44960</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44953</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46196</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45604</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45604</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45546</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45604</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>46290</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>44643</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>44896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45740</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45527</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45527</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45599</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45411</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45628</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>44982</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45268</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44817</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26830,7 +26830,7 @@
         <v>45442</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44935</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>44784</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>44784</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45527</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>45268</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45526</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44811</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>44978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44965</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>44830</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45365</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45604</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45175</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>45664</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45264</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45232</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45171</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45596</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45783</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>45428</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45432</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45790</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45700</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>44071</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44585</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45182</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45391</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45952</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45951</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>46085</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>46065</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45524</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45846</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45904</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45951</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44672</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44742</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45939</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45215</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>45299</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44564</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45551</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45874</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46083</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>46146</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44529</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44781</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44789</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45147</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46211</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44864</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44549</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44688</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44725</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44500</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44725</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44572</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45268</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44630</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45604</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45604</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45561</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44956</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>44896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46026</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46027</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46030</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>46031</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46031</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>46031</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>46036</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46037</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44690</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>46042</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45365</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45666</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45118</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45443</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46045</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45462</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>45377</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>46051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45240</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45925</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45925</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>46057</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>46057</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45930</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45282</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45455</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>46065</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>46064</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45936</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45937</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45939</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45945</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>46076</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44727</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46076</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45945</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45811</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45232</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45951</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46077</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46083</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45552</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45954</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45435</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46087</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44609</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45960</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46092</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45964</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46093</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46094</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>46098</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>46098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45771</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45107</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44572</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45985</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>46113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45960</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45825</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>46119</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45992</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45604</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45264</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45638</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>46092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45063</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44960</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45190</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45561</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45170</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45574</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45365</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45811</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45574</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45411</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45670</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46014</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45855</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45855</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45569</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45567</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44732</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>46136</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45561</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45561</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>46073</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44882</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45236</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46071</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>46098</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>46087</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>46034</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45870</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>46069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>46051</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>44711</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45006</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>44830</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46091</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>46044</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46153</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44869</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45216</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45321</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45628</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46087</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45604</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45604</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>46163</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46163</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46163</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46164</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45638</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45604</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45527</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45527</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>44992</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45604</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45527</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45342</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45574</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45883</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45265</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>46010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45154</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>46076</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45268</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45330</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45411</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45411</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45576</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45411</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45411</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45398</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45628</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45526</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>46191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>45264</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45427</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45110</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45455</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>46211</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45432</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>46261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45366</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44691</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>46262</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>44908</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45005</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44532</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45469</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45665</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44595</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45644</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>46273</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46275</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46234</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>46275</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45638</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45719</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45163</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44817</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45334</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44739</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45622</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44784</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>46290</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45247</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45201</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>46290</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>46290</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>46293</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>46196</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45604</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45771</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46293</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44784</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45140</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46254</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44811</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45411</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45527</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45442</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44643</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45628</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45232</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44953</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45520</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45604</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>44788</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>44748</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45171</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45596</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45428</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45432</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44155</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45391</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>45720</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45951</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45247</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>44855</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>46065</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>45524</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>45846</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>45904</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>45951</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44672</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44742</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>46281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45939</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>45215</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>45299</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>44564</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>45098</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>45575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         <v>45551</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45939</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45874</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46083</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>46000</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>46146</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44529</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44781</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44789</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44804</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45147</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>46211</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44846</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44725</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44864</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44549</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44511</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44735</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44688</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44546</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44725</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>44500</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44502</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44601</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44491</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44725</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44572</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45268</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44630</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45604</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45604</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45107</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>44978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45561</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>45281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>45636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44956</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44924</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45700</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>44896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>46014</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45939</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46026</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>46027</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>46030</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>46031</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>46031</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>46031</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>46034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>46036</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>46036</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45198</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>46036</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46037</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44690</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>46042</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45911</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45365</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45666</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45118</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45443</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46045</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45462</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>45377</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>46051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>45804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45240</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>45804</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45811</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45925</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45925</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>46057</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>45929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>46057</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44585</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45930</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45282</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45455</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>46065</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>46064</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45936</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45937</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45939</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>45740</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45945</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>46076</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44727</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>46076</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45945</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45811</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>46076</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45232</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45951</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45951</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>46077</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>46083</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>45552</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>45954</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>45435</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44784</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>46087</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>45960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44609</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45960</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46092</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45964</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>46093</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46094</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>46098</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>46098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>45971</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45771</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45107</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>44572</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>45622</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45820</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45985</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45599</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>46113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45960</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45825</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15497,7 +15497,7 @@
         <v>46119</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>46076</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45992</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45993</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45604</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45264</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>45638</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45138</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>46092</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>45063</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44960</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45190</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46136</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>45561</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45170</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45566</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45574</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>45365</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45811</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45574</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45411</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45670</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46014</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44972</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45855</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46043</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45855</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45569</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45567</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44732</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>46136</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>45561</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18233,7 +18233,7 @@
         <v>45561</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>46073</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44882</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45236</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46071</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46140</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>46098</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>46087</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>46034</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>45811</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45870</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>46069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>46051</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>44711</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>45006</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>44830</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46091</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>44935</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>46044</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46153</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46153</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44869</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45216</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>45321</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45628</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45175</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>46087</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45604</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>45604</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>46163</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46163</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46163</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46163</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>46163</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45484</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46164</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45638</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45604</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>45527</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45527</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>44992</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45604</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45527</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45342</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45574</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45883</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45265</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>46010</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45154</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>46076</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45268</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45330</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45411</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45411</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>44840</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45576</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>45411</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45411</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45398</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>44965</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45628</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23360,7 +23360,7 @@
         <v>45526</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>46191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46092</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>45264</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45427</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45063</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>46204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45110</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>46066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>45455</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>46211</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45432</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>46261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45366</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44812</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44691</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>46262</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>46174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>44908</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>45005</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44532</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45469</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45665</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44595</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45644</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>46273</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>46275</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>46234</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>46275</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45638</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45719</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45163</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46283</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>44817</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45334</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>44739</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>44809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45622</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44784</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>46290</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45247</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45201</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>46290</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>46290</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26700,7 +26700,7 @@
         <v>46293</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>46196</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45604</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45771</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>46293</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>44784</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45140</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>46254</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>44811</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45411</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45527</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45442</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>44643</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>45628</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45232</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44953</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>45520</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45604</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>44788</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>44748</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45171</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45596</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45428</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45432</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>44155</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44071</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28986,7 +28986,7 @@
         <v>45182</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45391</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>45720</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45951</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46065</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46281</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45846</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44732</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45904</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44802</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>44742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45215</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44789</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45098</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>46146</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46146</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>46083</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44529</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>46279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44804</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44864</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44549</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44500</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44491</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44688</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44650</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45435</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>45527</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>44882</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45411</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45198</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45321</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45599</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45342</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45411</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45110</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44869</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45628</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45561</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45455</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45527</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45268</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45442</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45455</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44784</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44784</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>45411</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45883</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44956</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>45527</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45526</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44811</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44840</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45334</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45604</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44965</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44830</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44572</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45365</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45216</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>45604</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45175</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44595</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44609</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>44972</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>44572</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45138</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45171</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45783</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44585</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45428</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>45432</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44630</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45163</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45638</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45925</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45566</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45666</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45929</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45365</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45443</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45569</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45118</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45644</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45462</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45377</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45190</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45427</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45804</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44691</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45398</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45576</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45937</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45182</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45604</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45604</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44784</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45063</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45453</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45771</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45107</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45232</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45628</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45820</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45006</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45154</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>45622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45670</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45604</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45951</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>45954</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>45960</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45960</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45411</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45961</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>44727</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44711</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44748</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45005</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45201</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45855</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44896</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44732</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45098</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45870</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45366</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44812</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45273</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45875</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45264</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44788</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45236</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>46094</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>46094</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46098</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>46098</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45469</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45520</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46113</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44581</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46119</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46000</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45432</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44960</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46136</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45604</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45604</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46136</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46014</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45546</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45604</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>46073</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46027</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46026</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46031</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>46031</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>45561</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46031</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46014</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46036</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45561</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>46036</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46037</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45567</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45811</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45574</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44896</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>46042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45740</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>46140</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46069</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46045</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46045</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>46043</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>46087</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45911</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>46051</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45971</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46071</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46098</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>46057</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45811</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46064</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46065</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46044</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46076</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>46076</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46153</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>46076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46154</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46077</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46087</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>46093</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46092</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>46087</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>46164</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>46163</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46010</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>46076</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45953</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46190</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46191</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46092</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>46275</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>46234</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44809</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44739</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46290</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46293</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46300</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46254</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>46293</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>46261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>46262</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>46204</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>46163</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>44071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45391</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46065</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>45076</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46281</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45846</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>44732</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45904</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>44802</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>44742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44564</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>45411</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45215</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>45939</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>44896</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44789</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>44594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         <v>45939</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>44781</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45098</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46000</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>46146</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46146</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>46083</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44529</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         <v>46273</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>46279</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44804</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>44864</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44549</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44503</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         <v>44500</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44491</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>44688</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>44650</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45719</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>45435</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>45527</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>44882</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45411</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>45198</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45321</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>45599</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45342</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45411</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45110</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44869</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45628</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45561</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>45411</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>44924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45455</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45527</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44982</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45268</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>45140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44817</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45442</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>45455</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44935</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>45281</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44784</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44784</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>45411</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45883</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44956</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>45527</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>45526</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44811</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44840</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44978</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45334</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45604</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44965</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>44830</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44572</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45365</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>45216</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>45604</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45175</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         <v>45664</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44595</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44609</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45264</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45905</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11975,7 +11975,7 @@
         <v>44972</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12048,7 +12048,7 @@
         <v>44572</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>45232</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45138</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45911</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45171</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45783</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44585</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45428</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>45432</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44630</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45163</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>45638</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45925</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45925</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45566</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45930</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45700</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45666</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45929</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45365</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45443</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45569</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45118</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45644</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45462</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45377</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>45604</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>45190</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45427</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45063</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45804</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44691</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45804</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45398</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45576</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45937</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45182</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45604</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45604</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>44784</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>45552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45063</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45453</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45945</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>45771</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>45107</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45232</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>45240</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45628</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45628</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45820</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45006</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45154</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45622</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>45574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>45636</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>45622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45825</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45670</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45604</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>45951</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45951</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>45954</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>45960</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45960</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45411</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45961</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45964</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>44727</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44711</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>45971</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>44748</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45005</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45201</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45855</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44896</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>44732</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>45098</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>45870</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45366</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>44812</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>45265</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>45273</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45875</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>44964</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45264</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44788</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45236</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>46094</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>46094</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46098</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>46098</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45985</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45469</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45520</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44532</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45960</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>45992</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46113</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44581</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46119</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46076</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46000</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>46092</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>46092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45432</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44960</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44953</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46136</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45604</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45604</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46136</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46014</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>46084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45546</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45604</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22262,7 +22262,7 @@
         <v>46073</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>46027</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>46026</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46030</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46031</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>46031</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45561</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>45561</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46031</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>44643</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>46034</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46014</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46036</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>46036</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45561</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>46036</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46037</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45567</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45811</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45574</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>44896</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>46042</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45740</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>46140</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46069</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46045</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>46045</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>46043</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>46087</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45911</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>46051</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45971</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46071</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46098</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>46057</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45811</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46091</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>46064</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>46065</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46044</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>46153</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46076</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>46076</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>46153</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>46076</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>46154</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>46083</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46077</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46087</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>46093</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46092</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>46087</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>46164</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46163</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>46163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>46163</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>46167</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46010</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         <v>46076</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45953</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>46190</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>46191</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>46092</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46211</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>46174</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>46275</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>46275</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>46234</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>46283</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27905,7 +27905,7 @@
         <v>44809</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>44739</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>46290</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>46196</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>46293</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>46300</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>46254</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>46293</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>46261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>46262</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>46204</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>46163</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>44071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45391</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29486,7 +29486,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46065</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46227</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46281</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44732</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45951</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>44672</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44802</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45411</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45215</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45299</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45610</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>45098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45551</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>46146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45931</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45874</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44781</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>46083</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>46273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45849</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44804</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45147</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46211</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44846</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44725</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>44864</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44549</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44735</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44688</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44725</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44500</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44601</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44491</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44630</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45604</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44581</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45664</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44978</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45561</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44956</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44924</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45198</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44690</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45240</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45455</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45740</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44727</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45232</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45435</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44572</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45599</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45574</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>46014</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>46043</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45604</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45638</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45567</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46136</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45561</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>46073</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45190</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46071</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46084</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45905</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45905</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>46051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45566</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45365</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45411</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45670</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46153</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>46153</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45937</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45939</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45569</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44732</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45236</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44896</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46154</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45951</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45951</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45960</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45961</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45960</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44711</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45006</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>46087</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45971</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44935</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>46163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46163</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>46164</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45985</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44869</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45216</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45321</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45628</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45993</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45604</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45604</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>46167</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45484</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45604</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45527</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45604</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45527</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45342</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45154</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>46014</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45268</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45411</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45411</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45939</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46026</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>46027</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46030</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46031</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46031</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46034</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>46036</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46036</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>46037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46076</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45576</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45411</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45411</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45398</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>46045</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>46045</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45628</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45526</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46051</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45264</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45427</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45063</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>46057</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>46057</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46065</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46064</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46076</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46076</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46076</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45110</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46087</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45455</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>46092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>46191</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46093</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>46094</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>46092</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>46094</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46098</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46098</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45432</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45366</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>44812</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44691</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46113</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44908</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45005</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46076</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44532</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>46092</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45469</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45665</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45638</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>46136</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45719</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45163</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44817</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45334</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45546</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45622</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>44784</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46275</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45247</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45201</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46234</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45604</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46283</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45771</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>44784</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45140</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44739</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45453</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44811</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45527</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45442</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44643</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46290</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45628</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45232</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>44953</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>44964</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45520</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45182</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45232</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44788</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>44748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45171</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45783</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45596</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45428</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45432</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45790</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46163</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>45365</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45666</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45118</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45443</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44809</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45462</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45377</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46261</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46300</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45804</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45811</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45552</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>44784</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45771</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45820</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>46293</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45825</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45855</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45855</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45870</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45875</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45883</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44155</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44071</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44585</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45391</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45720</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46065</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>46307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>46227</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>46281</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45846</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>44732</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>45951</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>44672</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44802</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>44803</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45411</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>45215</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>45299</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44564</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45610</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>45098</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45551</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>46146</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45931</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45939</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>45874</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44529</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>46000</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44781</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>46083</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>44789</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>46273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>46279</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44594</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45849</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>45853</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44804</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>45147</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>46211</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44846</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44725</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>44864</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>44549</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>44515</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44511</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>44735</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44688</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44546</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>44725</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>44500</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44601</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>44491</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>44715</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>44650</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>44748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         <v>44725</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44812</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44572</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>45268</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44630</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45604</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>44581</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45664</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>44978</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>45561</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>44956</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44924</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>44896</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9062,7 +9062,7 @@
         <v>45198</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44690</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45240</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>44585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45455</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45740</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44727</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45232</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45435</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>45107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>44572</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45599</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45811</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45574</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>46014</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>46043</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45604</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45264</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45638</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45145</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45567</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46136</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45561</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>46073</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45190</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>46071</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>46140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>46098</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46084</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46087</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>46034</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45905</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45905</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45170</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>46051</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45566</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45911</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45365</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46091</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45411</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45670</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>46044</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44972</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45098</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>46153</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>46153</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>45937</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45939</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>45569</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>44732</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45945</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>44882</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45236</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44896</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>46154</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45951</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45951</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45960</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>45961</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45960</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45964</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44711</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45006</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>46087</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45971</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44830</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44935</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>46163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>46163</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>46164</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45985</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44869</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45216</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45321</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45960</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45628</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45992</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45993</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45604</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45604</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>46167</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45484</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45604</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45527</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45527</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45604</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45527</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45342</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45574</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45265</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>45154</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>46014</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45268</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45411</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45411</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45939</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46026</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>46027</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>46030</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46031</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46031</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46031</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46034</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45953</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>46036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>46036</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46010</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>46036</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>46037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46076</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>45576</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45411</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45411</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45398</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>46045</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>46045</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45628</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45526</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>46051</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>45264</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45427</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45063</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>46057</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>46057</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46065</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46064</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46076</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46076</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46076</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46077</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46083</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>46190</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45110</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>46087</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21234,7 +21234,7 @@
         <v>45455</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>46092</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>46191</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>46093</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>46094</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>46092</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>46094</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46098</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46098</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45432</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45366</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>44812</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44691</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46113</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44908</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45005</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46076</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44532</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>46092</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45469</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>46092</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45665</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44595</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45638</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>46136</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>45719</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>45561</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45163</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45574</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44817</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45334</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>46066</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45546</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>46174</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>45622</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>44784</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>46275</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45247</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45201</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>46234</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>46275</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45604</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46283</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45771</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>44784</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>45140</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44739</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45453</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44811</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45527</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45442</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44643</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46290</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45628</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45232</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>44953</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>44964</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>46290</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45520</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46290</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45182</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45232</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>44788</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>44748</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45171</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45783</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45596</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45428</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45432</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45790</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46163</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>45365</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45666</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>46262</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45118</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45443</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46204</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44809</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45462</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45377</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>46261</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46300</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45804</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45804</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45811</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45811</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45552</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>44784</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45771</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45820</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>46293</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45825</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45855</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45855</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>45870</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28921,7 +28921,7 @@
         <v>45875</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45883</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44155</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44071</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44585</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45391</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45720</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45952</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>46281</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45846</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44732</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45904</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45781</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>44742</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45411</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45215</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44529</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45874</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>46083</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>46273</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44781</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>45716</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45551</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45098</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44804</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44864</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44549</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44688</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44725</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44500</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44725</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>45198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45321</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45110</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>45883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45604</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45604</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45905</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>46087</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>46164</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46163</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>46167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>44896</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45925</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45740</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45929</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45435</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45939</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44869</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>45945</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45527</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45527</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45411</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45455</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>44908</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>46076</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45951</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45951</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45954</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45411</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45628</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45961</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45455</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>46190</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44982</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45268</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44817</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45442</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44935</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45971</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44784</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44784</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45527</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>44811</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44978</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44965</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44830</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>46066</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45411</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45365</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45992</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>46211</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45604</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45175</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45993</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45232</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>46174</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45171</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45783</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45428</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46014</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46234</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45432</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45939</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46026</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46031</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>46031</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>46034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46283</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45666</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46036</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46036</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>46036</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45365</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>46037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45443</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>44739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45118</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45462</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46045</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46045</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45804</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>46057</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46057</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>46290</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45811</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45552</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45811</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46064</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46065</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45771</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45282</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46196</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46293</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46076</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>46077</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46087</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>46254</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>46093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46092</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>46094</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>46094</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46098</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44572</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45855</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46113</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>44866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46261</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45870</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46076</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44595</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46092</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46163</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>44809</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44972</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46262</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>46204</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45138</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>46136</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46293</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44585</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46136</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>46034</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>46084</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46073</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46314</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45561</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45561</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45638</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46014</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45566</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45561</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45567</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45811</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45574</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>46140</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45145</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45569</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46087</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45911</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46051</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46098</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46275</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>46275</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45811</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>46091</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45398</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45576</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>46153</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46153</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45170</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45604</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45604</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45453</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45628</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45628</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45006</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45638</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45638</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45636</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45604</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44748</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45201</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44896</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45098</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>44788</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45236</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44532</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45411</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45342</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45561</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45527</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45330</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45216</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44572</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45665</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45484</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45771</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44630</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45644</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45604</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45190</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45427</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45063</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44691</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45107</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45232</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45240</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45154</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45574</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45622</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45670</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44690</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44727</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44711</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44732</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45366</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>44812</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45273</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44964</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45469</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45520</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45232</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44581</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45432</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44960</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45391</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt SÄTER.xlsx
+++ b/Översikt SÄTER.xlsx
@@ -601,7 +601,7 @@
         <v>46065</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45852</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45524</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>45247</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>44855</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>45855</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46227</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>46281</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>45076</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>45846</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>44732</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45904</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45951</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44672</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45781</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>45281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>44742</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44802</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>44803</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>45411</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>45939</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>44564</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>45215</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45610</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>44789</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>44529</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45939</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45874</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>46000</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>46083</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45849</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45853</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>44594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>46273</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46146</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>46146</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44781</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>45716</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45551</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44896</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>45098</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>44804</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45147</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>46211</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44846</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44725</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44864</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44549</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44511</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44688</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44546</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44725</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>44500</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         <v>44502</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         <v>44650</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44748</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>44725</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7529,7 +7529,7 @@
         <v>44812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44953</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>44840</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>45411</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>45198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45321</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>45110</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         <v>45883</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         <v>45604</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45604</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>45719</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>45604</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>45905</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45905</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>46087</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>46164</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46163</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>46167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>44896</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44992</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45925</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45740</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45929</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45435</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45936</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45939</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44869</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>45945</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45527</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45527</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>45411</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45455</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>44908</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>46076</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45953</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>45599</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45951</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45951</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
         <v>45954</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45411</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45628</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45960</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45960</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>45961</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>45455</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>46190</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45964</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44982</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45268</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>46191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44817</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45442</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>46092</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44935</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45971</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44784</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44784</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45527</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45526</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>44811</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44978</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44965</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44830</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>46066</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45411</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45365</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45992</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>46211</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45604</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45175</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45993</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45664</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45232</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>46174</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45171</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45596</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45783</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45428</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46014</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>46234</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45432</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45939</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46026</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>46030</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46031</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>46031</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>46031</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>46034</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46283</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45700</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45666</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46036</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46036</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>46036</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45365</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>46037</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45443</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>44739</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45118</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45462</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45377</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>46045</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46045</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45971</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46051</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45804</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46290</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45804</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>46057</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46057</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>46290</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>46290</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>44784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45811</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45552</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45811</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46064</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46065</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45771</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45282</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46196</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46293</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45820</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46076</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>46076</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>46076</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>46083</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         <v>46077</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>46087</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>46254</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>46093</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46092</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>46094</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>46094</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>46098</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>44572</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45855</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45855</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46113</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>44866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46261</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45870</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46076</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45875</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44595</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44609</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46092</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46092</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46163</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>44809</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44972</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46262</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>46204</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>45138</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>46136</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46293</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44585</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>46136</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>46034</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>46084</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46073</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46314</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45561</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45561</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45638</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>46014</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>45566</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>45561</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>45574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>45567</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>45811</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45574</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>46140</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>46069</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45145</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>46043</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45569</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>46087</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45911</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46051</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46098</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>46275</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>46275</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45811</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>46091</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>46044</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45398</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45576</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>46153</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46153</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45170</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45182</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>45604</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>45604</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>45063</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45453</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45628</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45628</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45006</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45638</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45638</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45636</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45107</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45604</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45411</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44748</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45005</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45201</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44896</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45098</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25480,7 +25480,7 @@
         <v>44788</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45236</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44532</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45411</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45342</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45561</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45527</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45330</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45140</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>45216</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44572</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45665</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26444,7 +26444,7 @@
         <v>45484</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>45771</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>44630</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>45163</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26736,7 +26736,7 @@
         <v>45644</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45604</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45190</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45427</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45063</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>44691</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45107</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27257,7 +27257,7 @@
         <v>45232</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45240</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45154</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45574</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45622</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>45670</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44690</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44727</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>44711</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>45247</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44732</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
         <v>45366</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>44812</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>45265</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28294,7 +28294,7 @@
         <v>45273</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44964</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>45264</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45469</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>45520</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>45232</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>44581</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45432</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44960</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>44155</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44071</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>44585</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45391</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>45720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29407,7 +29407,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45951</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
